--- a/проработка.xlsx
+++ b/проработка.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>номер ктк</t>
   </si>
@@ -28,9 +28,6 @@
   </si>
   <si>
     <t>кол-во мест</t>
-  </si>
-  <si>
-    <t>CICU1400163/1</t>
   </si>
   <si>
     <t>Букинг</t>
@@ -46,7 +43,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,13 +58,6 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -147,21 +137,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -450,7 +437,7 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="3" max="3" width="22.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
@@ -461,13 +448,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -477,56 +464,60 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="5"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="5"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="5"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="5"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/проработка.xlsx
+++ b/проработка.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>номер ктк</t>
   </si>
@@ -37,13 +37,70 @@
   </si>
   <si>
     <t xml:space="preserve"> объем, м3</t>
+  </si>
+  <si>
+    <t>RLLCQG2607436</t>
+  </si>
+  <si>
+    <t>RLLSZN2607057</t>
+  </si>
+  <si>
+    <t>RLLCQG2607437</t>
+  </si>
+  <si>
+    <t>RLLSZN2607059</t>
+  </si>
+  <si>
+    <t>RLLSZN2608002</t>
+  </si>
+  <si>
+    <t>RLLSZN2607064</t>
+  </si>
+  <si>
+    <t>RLLQND2608201</t>
+  </si>
+  <si>
+    <t>ООО "СЕВЕРО-ЗАПАДНАЯ ИНСТРУМЕНТАЛЬНАЯ КОМПАНИЯ"</t>
+  </si>
+  <si>
+    <t>ООО “НЕОТЭК</t>
+  </si>
+  <si>
+    <t>ООО «РУСКОНТРАКТ»</t>
+  </si>
+  <si>
+    <t>ООО "ЦЕНТРЭКСИМ"</t>
+  </si>
+  <si>
+    <t>ООО "Техновуд"</t>
+  </si>
+  <si>
+    <t>XYLU8133686/1</t>
+  </si>
+  <si>
+    <t>XYLU8133686/2</t>
+  </si>
+  <si>
+    <t>XYLU8133686/3</t>
+  </si>
+  <si>
+    <t>XYLU8133686/4</t>
+  </si>
+  <si>
+    <t>XYLU8133686/5</t>
+  </si>
+  <si>
+    <t>XYLU8133686/6</t>
+  </si>
+  <si>
+    <t>XYLU8133686/7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,6 +115,13 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -92,7 +156,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -137,23 +201,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -437,7 +508,7 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="3" max="3" width="22.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
@@ -464,60 +535,144 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="A2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4">
+        <v>10.48</v>
+      </c>
+      <c r="E2" s="4">
+        <v>2400</v>
+      </c>
+      <c r="F2" s="4">
+        <v>80</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="A3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4">
+        <v>9.89</v>
+      </c>
+      <c r="E3" s="4">
+        <v>3836</v>
+      </c>
+      <c r="F3" s="4">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="A4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4">
+        <v>13.071999999999999</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1268</v>
+      </c>
+      <c r="F4" s="4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4">
+        <v>11.922000000000001</v>
+      </c>
+      <c r="E5" s="4">
+        <v>828</v>
+      </c>
+      <c r="F5" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="A6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="4">
+        <v>6.258</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1152</v>
+      </c>
+      <c r="F6" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4">
+        <v>5.98</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2919.54</v>
+      </c>
+      <c r="F7" s="4">
+        <v>256</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="A8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2732</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/проработка.xlsx
+++ b/проработка.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>номер ктк</t>
   </si>
@@ -30,6 +30,9 @@
     <t>кол-во мест</t>
   </si>
   <si>
+    <t>CICU1400163/1</t>
+  </si>
+  <si>
     <t>Букинг</t>
   </si>
   <si>
@@ -73,27 +76,6 @@
   </si>
   <si>
     <t>ООО "Техновуд"</t>
-  </si>
-  <si>
-    <t>XYLU8133686/1</t>
-  </si>
-  <si>
-    <t>XYLU8133686/2</t>
-  </si>
-  <si>
-    <t>XYLU8133686/3</t>
-  </si>
-  <si>
-    <t>XYLU8133686/4</t>
-  </si>
-  <si>
-    <t>XYLU8133686/5</t>
-  </si>
-  <si>
-    <t>XYLU8133686/6</t>
-  </si>
-  <si>
-    <t>XYLU8133686/7</t>
   </si>
 </sst>
 </file>
@@ -201,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -212,6 +194,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -221,10 +206,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -508,7 +489,7 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="3" max="3" width="22.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
@@ -519,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -535,142 +516,124 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="5">
+        <v>10.48</v>
+      </c>
+      <c r="E2" s="5">
+        <v>2400</v>
+      </c>
+      <c r="F2" s="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="5">
+        <v>9.89</v>
+      </c>
+      <c r="E3" s="5">
+        <v>3836</v>
+      </c>
+      <c r="F3" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5">
+        <v>13.071999999999999</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1268</v>
+      </c>
+      <c r="F4" s="5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="5">
+        <v>11.922000000000001</v>
+      </c>
+      <c r="E5" s="5">
+        <v>828</v>
+      </c>
+      <c r="F5" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5">
+        <v>6.258</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1152</v>
+      </c>
+      <c r="F6" s="5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5">
+        <v>5.98</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2919.54</v>
+      </c>
+      <c r="F7" s="5">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="4">
-        <v>10.48</v>
-      </c>
-      <c r="E2" s="4">
-        <v>2400</v>
-      </c>
-      <c r="F2" s="4">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4">
-        <v>9.89</v>
-      </c>
-      <c r="E3" s="4">
-        <v>3836</v>
-      </c>
-      <c r="F3" s="4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="4">
-        <v>13.071999999999999</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1268</v>
-      </c>
-      <c r="F4" s="4">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="4">
-        <v>11.922000000000001</v>
-      </c>
-      <c r="E5" s="4">
-        <v>828</v>
-      </c>
-      <c r="F5" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4">
-        <v>6.258</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1152</v>
-      </c>
-      <c r="F6" s="4">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="4">
-        <v>5.98</v>
-      </c>
-      <c r="E7" s="4">
-        <v>2919.54</v>
-      </c>
-      <c r="F7" s="4">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>5.6</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>2732</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>3</v>
       </c>
     </row>

--- a/проработка.xlsx
+++ b/проработка.xlsx
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -519,6 +519,302 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
